--- a/AAII_Financials/Quarterly/TCN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TCN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="92">
   <si>
     <t>TCN</t>
   </si>
@@ -656,251 +656,263 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:S102"/>
+  <dimension ref="A5:T102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>290900</v>
+        <v>306400</v>
       </c>
       <c r="E8" s="3">
-        <v>286400</v>
+        <v>286200</v>
       </c>
       <c r="F8" s="3">
-        <v>280100</v>
+        <v>281700</v>
       </c>
       <c r="G8" s="3">
-        <v>269200</v>
+        <v>275500</v>
       </c>
       <c r="H8" s="3">
-        <v>389500</v>
+        <v>264800</v>
       </c>
       <c r="I8" s="3">
-        <v>449400</v>
+        <v>383200</v>
       </c>
       <c r="J8" s="3">
+        <v>442100</v>
+      </c>
+      <c r="K8" s="3">
         <v>208000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>191900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>170200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>164500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>143000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>135300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>132400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>126500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>121600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>14900</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>92600</v>
+        <v>91400</v>
       </c>
       <c r="E9" s="3">
-        <v>89400</v>
+        <v>91100</v>
       </c>
       <c r="F9" s="3">
-        <v>85400</v>
+        <v>88000</v>
       </c>
       <c r="G9" s="3">
-        <v>80300</v>
+        <v>84000</v>
       </c>
       <c r="H9" s="3">
-        <v>74900</v>
+        <v>79000</v>
       </c>
       <c r="I9" s="3">
-        <v>132400</v>
+        <v>73700</v>
       </c>
       <c r="J9" s="3">
+        <v>130300</v>
+      </c>
+      <c r="K9" s="3">
         <v>62600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>55400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>53200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>48600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>43000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>47000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>44900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>46000</v>
       </c>
-      <c r="S9" s="3" t="s">
+      <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>198300</v>
+        <v>215000</v>
       </c>
       <c r="E10" s="3">
-        <v>197000</v>
+        <v>195100</v>
       </c>
       <c r="F10" s="3">
-        <v>194600</v>
+        <v>193800</v>
       </c>
       <c r="G10" s="3">
-        <v>188900</v>
+        <v>191500</v>
       </c>
       <c r="H10" s="3">
-        <v>314600</v>
+        <v>185800</v>
       </c>
       <c r="I10" s="3">
-        <v>317000</v>
+        <v>309500</v>
       </c>
       <c r="J10" s="3">
+        <v>311800</v>
+      </c>
+      <c r="K10" s="3">
         <v>145400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>136500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>117000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>115900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>88100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>85400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>81700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>75600</v>
       </c>
-      <c r="S10" s="3" t="s">
+      <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -920,8 +932,9 @@
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T11" s="3"/>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -973,8 +986,11 @@
       <c r="S12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1026,114 +1042,123 @@
       <c r="S13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>-1800</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H14" s="3">
-        <v>9400</v>
+        <v>0</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="s">
+        <v>9200</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>4700</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
+      <c r="O14" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>6900</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="E15" s="3">
-        <v>5900</v>
+        <v>6100</v>
       </c>
       <c r="F15" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="G15" s="3">
-        <v>6600</v>
+        <v>5800</v>
       </c>
       <c r="H15" s="3">
-        <v>5300</v>
+        <v>6400</v>
       </c>
       <c r="I15" s="3">
-        <v>9600</v>
+        <v>5200</v>
       </c>
       <c r="J15" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K15" s="3">
         <v>4700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>7700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>10300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>3500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>3400</v>
-      </c>
-      <c r="P15" s="3">
-        <v>3500</v>
       </c>
       <c r="Q15" s="3">
         <v>3500</v>
       </c>
       <c r="R15" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S15" s="3">
         <v>4300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1150,114 +1175,121 @@
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
-    </row>
-    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T16" s="3"/>
+    </row>
+    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>166100</v>
+        <v>351000</v>
       </c>
       <c r="E17" s="3">
-        <v>204300</v>
+        <v>163400</v>
       </c>
       <c r="F17" s="3">
-        <v>235400</v>
+        <v>201000</v>
       </c>
       <c r="G17" s="3">
-        <v>192400</v>
+        <v>231600</v>
       </c>
       <c r="H17" s="3">
-        <v>85600</v>
+        <v>189300</v>
       </c>
       <c r="I17" s="3">
-        <v>-455300</v>
+        <v>84200</v>
       </c>
       <c r="J17" s="3">
+        <v>-448000</v>
+      </c>
+      <c r="K17" s="3">
         <v>-83400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-9600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>-155800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>-102900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>57100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>4900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>42500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>78100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>194800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>22800</v>
       </c>
     </row>
-    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>124800</v>
+        <v>-44700</v>
       </c>
       <c r="E18" s="3">
-        <v>82100</v>
+        <v>122800</v>
       </c>
       <c r="F18" s="3">
-        <v>44700</v>
+        <v>80800</v>
       </c>
       <c r="G18" s="3">
-        <v>76800</v>
+        <v>43900</v>
       </c>
       <c r="H18" s="3">
-        <v>303900</v>
+        <v>75500</v>
       </c>
       <c r="I18" s="3">
-        <v>904700</v>
+        <v>299000</v>
       </c>
       <c r="J18" s="3">
+        <v>890100</v>
+      </c>
+      <c r="K18" s="3">
         <v>291300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>201600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>326000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>267400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>86000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>130400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>89900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>48400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-73100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-7900</v>
       </c>
     </row>
-    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1277,8 +1309,9 @@
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
-    </row>
-    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T19" s="3"/>
+    </row>
+    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1295,11 +1328,11 @@
         <v>0</v>
       </c>
       <c r="H20" s="3">
+        <v>0</v>
+      </c>
+      <c r="I20" s="3">
         <v>100</v>
       </c>
-      <c r="I20" s="3">
-        <v>0</v>
-      </c>
       <c r="J20" s="3">
         <v>0</v>
       </c>
@@ -1316,75 +1349,81 @@
         <v>0</v>
       </c>
       <c r="O20" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P20" s="3">
         <v>100</v>
       </c>
       <c r="Q20" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>77800</v>
       </c>
     </row>
-    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>131100</v>
+        <v>-38300</v>
       </c>
       <c r="E21" s="3">
-        <v>88000</v>
+        <v>128900</v>
       </c>
       <c r="F21" s="3">
-        <v>50600</v>
+        <v>86600</v>
       </c>
       <c r="G21" s="3">
-        <v>83300</v>
+        <v>49800</v>
       </c>
       <c r="H21" s="3">
-        <v>309300</v>
+        <v>82000</v>
       </c>
       <c r="I21" s="3">
-        <v>914400</v>
+        <v>304300</v>
       </c>
       <c r="J21" s="3">
+        <v>899500</v>
+      </c>
+      <c r="K21" s="3">
         <v>296000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>205400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>331200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>271400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>89500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>133800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>93400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>52000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-69600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>71900</v>
       </c>
     </row>
-    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1415,8 +1454,8 @@
       <c r="L22" s="3">
         <v>0</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>5</v>
+      <c r="M22" s="3">
+        <v>0</v>
       </c>
       <c r="N22" s="3" t="s">
         <v>5</v>
@@ -1433,117 +1472,126 @@
       <c r="R22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S22" s="3">
+      <c r="S22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T22" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>124900</v>
+        <v>-44700</v>
       </c>
       <c r="E23" s="3">
-        <v>82100</v>
+        <v>122800</v>
       </c>
       <c r="F23" s="3">
-        <v>44700</v>
+        <v>80800</v>
       </c>
       <c r="G23" s="3">
-        <v>76800</v>
+        <v>44000</v>
       </c>
       <c r="H23" s="3">
-        <v>304000</v>
+        <v>75500</v>
       </c>
       <c r="I23" s="3">
-        <v>904800</v>
+        <v>299100</v>
       </c>
       <c r="J23" s="3">
+        <v>890100</v>
+      </c>
+      <c r="K23" s="3">
         <v>291300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>201500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>326000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>267500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>86000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>130400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>89900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>48400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-73200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>58500</v>
       </c>
     </row>
-    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>13300</v>
+        <v>3300</v>
       </c>
       <c r="E24" s="3">
-        <v>17800</v>
+        <v>13000</v>
       </c>
       <c r="F24" s="3">
-        <v>4300</v>
+        <v>17500</v>
       </c>
       <c r="G24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="H24" s="3">
         <v>-100</v>
       </c>
-      <c r="H24" s="3">
-        <v>58100</v>
-      </c>
       <c r="I24" s="3">
-        <v>155500</v>
+        <v>57100</v>
       </c>
       <c r="J24" s="3">
+        <v>153000</v>
+      </c>
+      <c r="K24" s="3">
         <v>66500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>52400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>90700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>65200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>30200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>20500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-13900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1595,114 +1643,123 @@
       <c r="S25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>111600</v>
+        <v>-48000</v>
       </c>
       <c r="E26" s="3">
-        <v>64300</v>
+        <v>109800</v>
       </c>
       <c r="F26" s="3">
-        <v>40400</v>
+        <v>63300</v>
       </c>
       <c r="G26" s="3">
-        <v>76900</v>
+        <v>39800</v>
       </c>
       <c r="H26" s="3">
-        <v>245900</v>
+        <v>75600</v>
       </c>
       <c r="I26" s="3">
-        <v>749200</v>
+        <v>241900</v>
       </c>
       <c r="J26" s="3">
+        <v>737100</v>
+      </c>
+      <c r="K26" s="3">
         <v>224800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>149200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>235400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>202300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>55800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>98000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>69400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>38400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-59300</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>57700</v>
       </c>
     </row>
-    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>110300</v>
+        <v>-51800</v>
       </c>
       <c r="E27" s="3">
-        <v>62400</v>
+        <v>108500</v>
       </c>
       <c r="F27" s="3">
-        <v>37100</v>
+        <v>61300</v>
       </c>
       <c r="G27" s="3">
-        <v>73400</v>
+        <v>36500</v>
       </c>
       <c r="H27" s="3">
-        <v>244700</v>
+        <v>72200</v>
       </c>
       <c r="I27" s="3">
-        <v>746300</v>
+        <v>240800</v>
       </c>
       <c r="J27" s="3">
+        <v>734200</v>
+      </c>
+      <c r="K27" s="3">
         <v>223300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>146700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>234000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>201200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>55000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>95600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>68800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>38100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-59900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1754,8 +1811,11 @@
       <c r="S28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1769,46 +1829,49 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>2500</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-3200</v>
       </c>
-      <c r="I29" s="3">
-        <v>49000</v>
-      </c>
       <c r="J29" s="3">
-        <v>0</v>
+        <v>48200</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>22300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>37200</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-90000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>7300</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>6400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>-16300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>7700</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1860,8 +1923,11 @@
       <c r="S30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1913,8 +1979,11 @@
       <c r="S31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1931,11 +2000,11 @@
         <v>0</v>
       </c>
       <c r="H32" s="3">
+        <v>0</v>
+      </c>
+      <c r="I32" s="3">
         <v>-100</v>
       </c>
-      <c r="I32" s="3">
-        <v>0</v>
-      </c>
       <c r="J32" s="3">
         <v>0</v>
       </c>
@@ -1952,75 +2021,81 @@
         <v>0</v>
       </c>
       <c r="O32" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P32" s="3">
         <v>-100</v>
       </c>
       <c r="Q32" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-77800</v>
       </c>
     </row>
-    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>110300</v>
+        <v>-51800</v>
       </c>
       <c r="E33" s="3">
-        <v>62400</v>
+        <v>108500</v>
       </c>
       <c r="F33" s="3">
-        <v>37100</v>
+        <v>61300</v>
       </c>
       <c r="G33" s="3">
-        <v>75900</v>
+        <v>36500</v>
       </c>
       <c r="H33" s="3">
-        <v>241500</v>
+        <v>74700</v>
       </c>
       <c r="I33" s="3">
-        <v>795300</v>
+        <v>237600</v>
       </c>
       <c r="J33" s="3">
+        <v>782400</v>
+      </c>
+      <c r="K33" s="3">
         <v>223300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>169000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>271100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>201200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-34900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>103000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>75100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>21700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-52200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2072,119 +2147,128 @@
       <c r="S34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>110300</v>
+        <v>-51800</v>
       </c>
       <c r="E35" s="3">
-        <v>62400</v>
+        <v>108500</v>
       </c>
       <c r="F35" s="3">
-        <v>37100</v>
+        <v>61300</v>
       </c>
       <c r="G35" s="3">
-        <v>75900</v>
+        <v>36500</v>
       </c>
       <c r="H35" s="3">
-        <v>241500</v>
+        <v>74700</v>
       </c>
       <c r="I35" s="3">
-        <v>795300</v>
+        <v>237600</v>
       </c>
       <c r="J35" s="3">
+        <v>782400</v>
+      </c>
+      <c r="K35" s="3">
         <v>223300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>169000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>271100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>201200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-34900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>103000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>75100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>21700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-52200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2204,8 +2288,9 @@
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
-    </row>
-    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T39" s="3"/>
+    </row>
+    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2225,61 +2310,65 @@
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
-    </row>
-    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T40" s="3"/>
+    </row>
+    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>237700</v>
+        <v>231000</v>
       </c>
       <c r="E41" s="3">
-        <v>165600</v>
+        <v>233800</v>
       </c>
       <c r="F41" s="3">
-        <v>195800</v>
+        <v>162900</v>
       </c>
       <c r="G41" s="3">
-        <v>281000</v>
+        <v>192700</v>
       </c>
       <c r="H41" s="3">
-        <v>195200</v>
+        <v>276500</v>
       </c>
       <c r="I41" s="3">
-        <v>201500</v>
+        <v>192000</v>
       </c>
       <c r="J41" s="3">
+        <v>198200</v>
+      </c>
+      <c r="K41" s="3">
         <v>197000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>238900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>203600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>117200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>392500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>69100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>42600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>67700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11300</v>
       </c>
     </row>
-    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2331,61 +2420,67 @@
       <c r="S42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>53200</v>
+        <v>37800</v>
       </c>
       <c r="E43" s="3">
-        <v>34800</v>
+        <v>52300</v>
       </c>
       <c r="F43" s="3">
-        <v>31100</v>
+        <v>34300</v>
       </c>
       <c r="G43" s="3">
-        <v>34400</v>
+        <v>30600</v>
       </c>
       <c r="H43" s="3">
-        <v>163000</v>
+        <v>33800</v>
       </c>
       <c r="I43" s="3">
-        <v>24200</v>
+        <v>160300</v>
       </c>
       <c r="J43" s="3">
+        <v>23800</v>
+      </c>
+      <c r="K43" s="3">
         <v>58700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>27400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>41100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>54300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>33100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>28200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>22600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>16400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>11400</v>
       </c>
     </row>
-    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2437,167 +2532,179 @@
       <c r="S44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>32100</v>
+        <v>99100</v>
       </c>
       <c r="E45" s="3">
-        <v>44400</v>
+        <v>31600</v>
       </c>
       <c r="F45" s="3">
-        <v>60600</v>
+        <v>43700</v>
       </c>
       <c r="G45" s="3">
-        <v>51600</v>
+        <v>59700</v>
       </c>
       <c r="H45" s="3">
-        <v>343800</v>
+        <v>50800</v>
       </c>
       <c r="I45" s="3">
-        <v>74700</v>
+        <v>338300</v>
       </c>
       <c r="J45" s="3">
+        <v>73500</v>
+      </c>
+      <c r="K45" s="3">
         <v>60300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>40600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>20800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>23600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>14400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>16300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>25800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>1000</v>
       </c>
     </row>
-    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>323000</v>
+        <v>368000</v>
       </c>
       <c r="E46" s="3">
-        <v>244800</v>
+        <v>317700</v>
       </c>
       <c r="F46" s="3">
-        <v>287600</v>
+        <v>240800</v>
       </c>
       <c r="G46" s="3">
-        <v>367000</v>
+        <v>282900</v>
       </c>
       <c r="H46" s="3">
-        <v>702000</v>
+        <v>361000</v>
       </c>
       <c r="I46" s="3">
-        <v>300300</v>
+        <v>690700</v>
       </c>
       <c r="J46" s="3">
+        <v>295500</v>
+      </c>
+      <c r="K46" s="3">
         <v>316000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>339600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>271500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>179100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>470400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>122000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>111700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>81500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>109900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>23800</v>
       </c>
     </row>
-    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>17298600</v>
+        <v>17140700</v>
       </c>
       <c r="E47" s="3">
-        <v>17020600</v>
+        <v>17018200</v>
       </c>
       <c r="F47" s="3">
-        <v>16491000</v>
+        <v>16744600</v>
       </c>
       <c r="G47" s="3">
-        <v>16296600</v>
+        <v>16223700</v>
       </c>
       <c r="H47" s="3">
-        <v>15797600</v>
+        <v>16032400</v>
       </c>
       <c r="I47" s="3">
-        <v>14938400</v>
+        <v>15541500</v>
       </c>
       <c r="J47" s="3">
+        <v>14696200</v>
+      </c>
+      <c r="K47" s="3">
         <v>13153900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11552200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10205700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8965200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>7689900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8648300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8305700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7913000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7771300</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>2791600</v>
       </c>
     </row>
-    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -2610,100 +2717,106 @@
       <c r="F48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G48" s="3">
-        <v>133200</v>
-      </c>
-      <c r="H48" s="3" t="s">
+      <c r="G48" s="3" t="s">
         <v>5</v>
+      </c>
+      <c r="H48" s="3">
+        <v>131100</v>
       </c>
       <c r="I48" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="J48" s="3">
+      <c r="J48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K48" s="3">
         <v>123400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>114500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>109800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>113500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>62000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>59900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>56800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>56100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>39100</v>
       </c>
     </row>
-    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>48600</v>
+        <v>47200</v>
       </c>
       <c r="E49" s="3">
-        <v>49300</v>
+        <v>47800</v>
       </c>
       <c r="F49" s="3">
-        <v>49900</v>
+        <v>48500</v>
       </c>
       <c r="G49" s="3">
+        <v>49100</v>
+      </c>
+      <c r="H49" s="3">
+        <v>49800</v>
+      </c>
+      <c r="I49" s="3">
         <v>50600</v>
       </c>
-      <c r="H49" s="3">
-        <v>51400</v>
-      </c>
-      <c r="I49" s="3">
-        <v>52100</v>
-      </c>
       <c r="J49" s="3">
+        <v>51300</v>
+      </c>
+      <c r="K49" s="3">
         <v>52900</v>
-      </c>
-      <c r="K49" s="3">
-        <v>52700</v>
       </c>
       <c r="L49" s="3">
         <v>52700</v>
       </c>
       <c r="M49" s="3">
+        <v>52700</v>
+      </c>
+      <c r="N49" s="3">
         <v>55800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>54700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>156600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>159400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>157000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>158200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>21200</v>
       </c>
     </row>
-    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2755,8 +2868,11 @@
       <c r="S50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2808,61 +2924,67 @@
       <c r="S51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>462100</v>
+        <v>371800</v>
       </c>
       <c r="E52" s="3">
-        <v>476300</v>
+        <v>454600</v>
       </c>
       <c r="F52" s="3">
-        <v>420500</v>
+        <v>468600</v>
       </c>
       <c r="G52" s="3">
-        <v>278800</v>
+        <v>413700</v>
       </c>
       <c r="H52" s="3">
-        <v>513900</v>
+        <v>274300</v>
       </c>
       <c r="I52" s="3">
-        <v>509900</v>
+        <v>505600</v>
       </c>
       <c r="J52" s="3">
+        <v>501600</v>
+      </c>
+      <c r="K52" s="3">
         <v>338700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>298000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>291800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>251300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>209000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>283800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>277300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>249700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>236300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>57000</v>
       </c>
     </row>
-    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2914,61 +3036,67 @@
       <c r="S53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>18132300</v>
+        <v>17927800</v>
       </c>
       <c r="E54" s="3">
-        <v>17790900</v>
+        <v>17838300</v>
       </c>
       <c r="F54" s="3">
-        <v>17249000</v>
+        <v>17502500</v>
       </c>
       <c r="G54" s="3">
-        <v>17126300</v>
+        <v>16969400</v>
       </c>
       <c r="H54" s="3">
-        <v>17064900</v>
+        <v>16848600</v>
       </c>
       <c r="I54" s="3">
-        <v>15800800</v>
+        <v>16788300</v>
       </c>
       <c r="J54" s="3">
+        <v>15544600</v>
+      </c>
+      <c r="K54" s="3">
         <v>13984800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>12357000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10931500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9565000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8492300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9272800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8913900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8458000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8331700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>2932700</v>
       </c>
     </row>
-    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2988,8 +3116,9 @@
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
-    </row>
-    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T55" s="3"/>
+    </row>
+    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3009,326 +3138,345 @@
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
-    </row>
-    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T56" s="3"/>
+    </row>
+    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>282500</v>
+        <v>203300</v>
       </c>
       <c r="E57" s="3">
-        <v>211300</v>
+        <v>277900</v>
       </c>
       <c r="F57" s="3">
-        <v>174300</v>
+        <v>207900</v>
       </c>
       <c r="G57" s="3">
-        <v>47100</v>
+        <v>171400</v>
       </c>
       <c r="H57" s="3">
-        <v>272600</v>
+        <v>46300</v>
       </c>
       <c r="I57" s="3">
-        <v>179000</v>
+        <v>268200</v>
       </c>
       <c r="J57" s="3">
+        <v>176100</v>
+      </c>
+      <c r="K57" s="3">
         <v>64500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>58700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>62300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>45300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>39400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>40300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>85500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>74200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>859600</v>
+        <v>418300</v>
       </c>
       <c r="E58" s="3">
-        <v>1102500</v>
+        <v>845700</v>
       </c>
       <c r="F58" s="3">
-        <v>1327400</v>
+        <v>1084700</v>
       </c>
       <c r="G58" s="3">
-        <v>1046400</v>
+        <v>1305900</v>
       </c>
       <c r="H58" s="3">
-        <v>660700</v>
+        <v>1029400</v>
       </c>
       <c r="I58" s="3">
-        <v>475000</v>
+        <v>650000</v>
       </c>
       <c r="J58" s="3">
+        <v>467300</v>
+      </c>
+      <c r="K58" s="3">
         <v>355600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>346600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>662600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>269400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>192500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>356700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>177400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>168600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>179000</v>
       </c>
-      <c r="S58" s="3" t="s">
+      <c r="T58" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>137100</v>
+        <v>136700</v>
       </c>
       <c r="E59" s="3">
-        <v>129000</v>
+        <v>134900</v>
       </c>
       <c r="F59" s="3">
-        <v>130600</v>
+        <v>127000</v>
       </c>
       <c r="G59" s="3">
-        <v>269800</v>
+        <v>128500</v>
       </c>
       <c r="H59" s="3">
-        <v>190100</v>
+        <v>265500</v>
       </c>
       <c r="I59" s="3">
-        <v>111700</v>
+        <v>187000</v>
       </c>
       <c r="J59" s="3">
+        <v>109900</v>
+      </c>
+      <c r="K59" s="3">
         <v>184300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>175900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>193200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>191000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>136800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>156500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>185500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>98200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>81500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>1279300</v>
+        <v>758300</v>
       </c>
       <c r="E60" s="3">
-        <v>1442900</v>
+        <v>1258500</v>
       </c>
       <c r="F60" s="3">
-        <v>1632200</v>
+        <v>1419500</v>
       </c>
       <c r="G60" s="3">
-        <v>1363300</v>
+        <v>1605800</v>
       </c>
       <c r="H60" s="3">
-        <v>1123400</v>
+        <v>1341200</v>
       </c>
       <c r="I60" s="3">
-        <v>765700</v>
+        <v>1105200</v>
       </c>
       <c r="J60" s="3">
+        <v>753300</v>
+      </c>
+      <c r="K60" s="3">
         <v>604400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>581300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>918200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>505700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>368700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>553500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>397800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>352400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>334700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>46500</v>
       </c>
     </row>
-    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>7322400</v>
+        <v>7755600</v>
       </c>
       <c r="E61" s="3">
-        <v>7270300</v>
+        <v>7203700</v>
       </c>
       <c r="F61" s="3">
-        <v>6887300</v>
+        <v>7152400</v>
       </c>
       <c r="G61" s="3">
-        <v>7190900</v>
+        <v>6775600</v>
       </c>
       <c r="H61" s="3">
-        <v>7467400</v>
+        <v>7074400</v>
       </c>
       <c r="I61" s="3">
-        <v>6884900</v>
+        <v>7346400</v>
       </c>
       <c r="J61" s="3">
+        <v>6773300</v>
+      </c>
+      <c r="K61" s="3">
         <v>6041000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5293400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4825800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4879800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4809100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5538600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5536900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5293000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5225000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>599400</v>
       </c>
     </row>
-    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>4166600</v>
+        <v>4177600</v>
       </c>
       <c r="E62" s="3">
-        <v>3797900</v>
+        <v>4099100</v>
       </c>
       <c r="F62" s="3">
-        <v>3503300</v>
+        <v>3736300</v>
       </c>
       <c r="G62" s="3">
-        <v>3349200</v>
+        <v>3446500</v>
       </c>
       <c r="H62" s="3">
-        <v>3303600</v>
+        <v>3294900</v>
       </c>
       <c r="I62" s="3">
-        <v>3179200</v>
+        <v>3250000</v>
       </c>
       <c r="J62" s="3">
+        <v>3127700</v>
+      </c>
+      <c r="K62" s="3">
         <v>2910000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2347800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1947700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1401400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1038900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>927700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>805100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>755900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>731900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>170700</v>
       </c>
     </row>
-    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3380,8 +3528,11 @@
       <c r="S63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3433,8 +3584,11 @@
       <c r="S64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3486,61 +3640,67 @@
       <c r="S65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12773700</v>
+        <v>12699300</v>
       </c>
       <c r="E66" s="3">
-        <v>12517500</v>
+        <v>12566600</v>
       </c>
       <c r="F66" s="3">
-        <v>12028000</v>
+        <v>12314600</v>
       </c>
       <c r="G66" s="3">
-        <v>11912800</v>
+        <v>11833000</v>
       </c>
       <c r="H66" s="3">
-        <v>11901600</v>
+        <v>11719700</v>
       </c>
       <c r="I66" s="3">
-        <v>10837500</v>
+        <v>11708600</v>
       </c>
       <c r="J66" s="3">
+        <v>10661800</v>
+      </c>
+      <c r="K66" s="3">
         <v>9564000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>8232300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7699000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6795200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6225400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7030300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6750600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6411200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6301200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>826900</v>
       </c>
     </row>
-    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3560,8 +3720,9 @@
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
-    </row>
-    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T67" s="3"/>
+    </row>
+    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3774,11 @@
       <c r="S68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3666,8 +3830,11 @@
       <c r="S69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3719,8 +3886,11 @@
       <c r="S70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3772,61 +3942,67 @@
       <c r="S71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>2395300</v>
+        <v>2283300</v>
       </c>
       <c r="E72" s="3">
-        <v>2306800</v>
+        <v>2356500</v>
       </c>
       <c r="F72" s="3">
-        <v>2266200</v>
+        <v>2269400</v>
       </c>
       <c r="G72" s="3">
-        <v>2253200</v>
+        <v>2229500</v>
       </c>
       <c r="H72" s="3">
-        <v>2200200</v>
+        <v>2216600</v>
       </c>
       <c r="I72" s="3">
-        <v>1980500</v>
+        <v>2164500</v>
       </c>
       <c r="J72" s="3">
+        <v>1948400</v>
+      </c>
+      <c r="K72" s="3">
         <v>1430300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>1206700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>1058500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>823600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>615300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>644900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>560800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>487400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>478100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>525400</v>
       </c>
     </row>
-    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3878,8 +4054,11 @@
       <c r="S73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3931,8 +4110,11 @@
       <c r="S74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3984,61 +4166,67 @@
       <c r="S75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>5358600</v>
+        <v>5228400</v>
       </c>
       <c r="E76" s="3">
-        <v>5273400</v>
+        <v>5271700</v>
       </c>
       <c r="F76" s="3">
-        <v>5221000</v>
+        <v>5187900</v>
       </c>
       <c r="G76" s="3">
-        <v>5213500</v>
+        <v>5136300</v>
       </c>
       <c r="H76" s="3">
-        <v>5163400</v>
+        <v>5129000</v>
       </c>
       <c r="I76" s="3">
-        <v>4963300</v>
+        <v>5079700</v>
       </c>
       <c r="J76" s="3">
+        <v>4882800</v>
+      </c>
+      <c r="K76" s="3">
         <v>4420900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4124800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3232500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>2769900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2266900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2242400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2163300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2046800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2030500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2105800</v>
       </c>
     </row>
-    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4090,119 +4278,128 @@
       <c r="S77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="T77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
     </row>
-    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>110300</v>
+        <v>-51800</v>
       </c>
       <c r="E81" s="3">
-        <v>62400</v>
+        <v>108500</v>
       </c>
       <c r="F81" s="3">
-        <v>37100</v>
+        <v>61300</v>
       </c>
       <c r="G81" s="3">
-        <v>75900</v>
+        <v>36500</v>
       </c>
       <c r="H81" s="3">
-        <v>241500</v>
+        <v>74700</v>
       </c>
       <c r="I81" s="3">
-        <v>795300</v>
+        <v>237600</v>
       </c>
       <c r="J81" s="3">
+        <v>782400</v>
+      </c>
+      <c r="K81" s="3">
         <v>223300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>169000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>271100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>201200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-34900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>103000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>75100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>21700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-52200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>56100</v>
       </c>
     </row>
-    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4222,49 +4419,50 @@
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
-    </row>
-    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T82" s="3"/>
+    </row>
+    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6200</v>
+        <v>6400</v>
       </c>
       <c r="E83" s="3">
-        <v>5900</v>
+        <v>6100</v>
       </c>
       <c r="F83" s="3">
-        <v>5900</v>
+        <v>5800</v>
       </c>
       <c r="G83" s="3">
-        <v>6600</v>
+        <v>5800</v>
       </c>
       <c r="H83" s="3">
-        <v>5300</v>
+        <v>6400</v>
       </c>
       <c r="I83" s="3">
-        <v>9600</v>
+        <v>5200</v>
       </c>
       <c r="J83" s="3">
+        <v>9500</v>
+      </c>
+      <c r="K83" s="3">
         <v>4700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>5100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3400</v>
-      </c>
-      <c r="P83" s="3">
-        <v>3500</v>
       </c>
       <c r="Q83" s="3">
         <v>3500</v>
@@ -4273,10 +4471,13 @@
         <v>3500</v>
       </c>
       <c r="S83" s="3">
+        <v>3500</v>
+      </c>
+      <c r="T83" s="3">
         <v>2000</v>
       </c>
     </row>
-    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4328,8 +4529,11 @@
       <c r="S84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4381,8 +4585,11 @@
       <c r="S85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4434,8 +4641,11 @@
       <c r="S86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4487,8 +4697,11 @@
       <c r="S87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4540,61 +4753,67 @@
       <c r="S88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>103400</v>
+        <v>-16100</v>
       </c>
       <c r="E89" s="3">
-        <v>79300</v>
+        <v>101700</v>
       </c>
       <c r="F89" s="3">
-        <v>23600</v>
+        <v>78000</v>
       </c>
       <c r="G89" s="3">
-        <v>30500</v>
+        <v>23200</v>
       </c>
       <c r="H89" s="3">
-        <v>147300</v>
+        <v>30000</v>
       </c>
       <c r="I89" s="3">
-        <v>194000</v>
+        <v>144900</v>
       </c>
       <c r="J89" s="3">
+        <v>190800</v>
+      </c>
+      <c r="K89" s="3">
         <v>53200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>86600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>21400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>56100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>61800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>44600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>45000</v>
       </c>
     </row>
-    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4614,61 +4833,65 @@
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
-    </row>
-    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T90" s="3"/>
+    </row>
+    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-10600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-18900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-1700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-8100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4720,8 +4943,11 @@
       <c r="S92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4773,61 +4999,67 @@
       <c r="S93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-172600</v>
+        <v>-103800</v>
       </c>
       <c r="E94" s="3">
-        <v>-342200</v>
+        <v>-169800</v>
       </c>
       <c r="F94" s="3">
-        <v>-178400</v>
+        <v>-336600</v>
       </c>
       <c r="G94" s="3">
-        <v>-112600</v>
+        <v>-175500</v>
       </c>
       <c r="H94" s="3">
-        <v>-1003900</v>
+        <v>-110700</v>
       </c>
       <c r="I94" s="3">
-        <v>-2213100</v>
+        <v>-987600</v>
       </c>
       <c r="J94" s="3">
+        <v>-2177200</v>
+      </c>
+      <c r="K94" s="3">
         <v>-960300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-931100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-947200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-591000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>279700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-263100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-124200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-129100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2300</v>
       </c>
     </row>
-    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4847,61 +5079,65 @@
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
-    </row>
-    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T95" s="3"/>
+    </row>
+    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-8400</v>
+        <v>-2700</v>
       </c>
       <c r="E96" s="3">
-        <v>-22700</v>
+        <v>-8300</v>
       </c>
       <c r="F96" s="3">
-        <v>-17200</v>
+        <v>-22300</v>
       </c>
       <c r="G96" s="3">
-        <v>-3100</v>
+        <v>-16900</v>
       </c>
       <c r="H96" s="3">
-        <v>-9400</v>
+        <v>-3000</v>
       </c>
       <c r="I96" s="3">
-        <v>-38900</v>
+        <v>-9200</v>
       </c>
       <c r="J96" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="K96" s="3">
         <v>-16600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-50300</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
-      </c>
       <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3">
         <v>-1100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-11200</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-33700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1500</v>
       </c>
-      <c r="R96" s="3">
-        <v>0</v>
-      </c>
       <c r="S96" s="3">
+        <v>0</v>
+      </c>
+      <c r="T96" s="3">
         <v>-11600</v>
       </c>
     </row>
-    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4953,8 +5189,11 @@
       <c r="S97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5006,8 +5245,11 @@
       <c r="S98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5059,163 +5301,175 @@
       <c r="S99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>141400</v>
+        <v>116900</v>
       </c>
       <c r="E100" s="3">
-        <v>232500</v>
+        <v>139100</v>
       </c>
       <c r="F100" s="3">
-        <v>69600</v>
+        <v>228700</v>
       </c>
       <c r="G100" s="3">
-        <v>167800</v>
+        <v>68500</v>
       </c>
       <c r="H100" s="3">
-        <v>850600</v>
+        <v>165100</v>
       </c>
       <c r="I100" s="3">
-        <v>1977400</v>
+        <v>836800</v>
       </c>
       <c r="J100" s="3">
+        <v>1945300</v>
+      </c>
+      <c r="K100" s="3">
         <v>860700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>965500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>956700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>242800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>23000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>244400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>92200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-36700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>142300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-41100</v>
       </c>
     </row>
-    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>100</v>
       </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
       <c r="G101" s="3">
+        <v>0</v>
+      </c>
+      <c r="H101" s="3">
         <v>100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>100</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-100</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>100</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-100</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
+      <c r="T101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>72100</v>
+        <v>-2800</v>
       </c>
       <c r="E102" s="3">
-        <v>-30300</v>
+        <v>70900</v>
       </c>
       <c r="F102" s="3">
-        <v>-85200</v>
+        <v>-29800</v>
       </c>
       <c r="G102" s="3">
-        <v>85800</v>
+        <v>-83800</v>
       </c>
       <c r="H102" s="3">
-        <v>-6300</v>
+        <v>84400</v>
       </c>
       <c r="I102" s="3">
-        <v>-41900</v>
+        <v>-6100</v>
       </c>
       <c r="J102" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="K102" s="3">
         <v>-46400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>35300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>89100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-290300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>319000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>25500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-25100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>56400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
     </row>
